--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_修正が要る箇所_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_修正が要る箇所_20260925.xlsx
@@ -1202,7 +1202,7 @@
         <v>6104</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>6095</v>
+        <v>6048</v>
       </c>
     </row>
   </sheetData>
@@ -1778,7 +1778,7 @@
         <v>3093948</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>6095</v>
+        <v>6048</v>
       </c>
     </row>
   </sheetData>
